--- a/login-app/docs/specs-and-testcases.xlsx
+++ b/login-app/docs/specs-and-testcases.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>failed_login_count &gt;= 5, locked_until が設定</t>
+          <t>ログイン連続失敗回数が5回に達し、ロック期限が設定される</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>locked_until = 9999-12-31（永続）</t>
+          <t>ロック期限が永続（9999-12-31）に設定される</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>is_active = false</t>
+          <t>アカウントが無効化される</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>locked_until が過去になる / failed_login_count = 0</t>
+          <t>ロック期限が過去になり、失敗回数がリセットされる</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>locked_until = NULL, failed_login_count = 0</t>
+          <t>ロック期限が解除され、失敗回数がリセットされる</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>is_active = true</t>
+          <t>アカウントが有効化される</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>password_changed_at = NOW()</t>
+          <t>パスワード変更日時が現在時刻に更新される</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>force_password_change フラグ → 次回ログイン時に変更画面へ</t>
+          <t>次回ログイン時にパスワード変更画面へ誘導される</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>is_admin=true は変化しない。パスワードのみ更新</t>
+          <t>管理者フラグは変化しない。パスワードのみ更新される</t>
         </is>
       </c>
     </row>
@@ -2136,8 +2136,8 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>1. #screen-home が display:flex になる
-2. #home-username のテキストが「user001 さん」
+          <t>1. ホーム画面に切り替わる
+2. ホーム画面のユーザー名表示が「user001 さん」になる
 3. ログイン成功メッセージが表示される</t>
         </is>
       </c>
@@ -2239,9 +2239,9 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>1. #err-userid が visible になる
+          <t>1. ユーザーIDエラーメッセージが表示される
 2. エラー文言が「ユーザーIDを入力してください」
-3. #user-id に error クラスが付く
+3. ユーザーID入力欄がエラー表示になる
 4. API 呼び出しは発生しない</t>
         </is>
       </c>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>1. #err-password が visible になる
+          <t>1. パスワードエラーメッセージが表示される
 2. エラー文言が「パスワードを入力してください」
 3. API 呼び出しは発生しない</t>
         </is>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>1. #err-userid が visible になる
+          <t>1. ユーザーIDエラーメッセージが表示される
 2. エラー文言が「ユーザーIDは半角英数字で入力してください」</t>
         </is>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>1. #err-password が visible になる
+          <t>1. パスワードエラーメッセージが表示される
 2. エラー文言が「パスワードは8〜32文字で入力してください」</t>
         </is>
       </c>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>1. #err-password に visible クラスがない
+          <t>1. パスワードエラーメッセージが表示されない
 2. エラーメッセージが表示されない</t>
         </is>
       </c>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態で存在する（failed_login_count = 0）</t>
+          <t>・user001 が有効状態で存在する（ログイン失敗回数がゼロの状態）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2487,9 +2487,9 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>1. #auth-error が visible になる
+          <t>1. 認証エラーメッセージが表示される
 2. テキストに「あと4回失敗するとロックされます」が含まれる
-3. auth-locked クラスは付かない</t>
+3. ロックエラー表示にはなっていない</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>・e2elock が有効状態で存在する（failed_login_count = 0）</t>
+          <t>・e2elock が有効状態で存在する（ログイン失敗回数がゼロの状態）</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2540,8 +2540,8 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>1. 1〜4回目：#auth-error に残り回数（4,3,2,1）が表示される
-2. 5回目：#auth-error に auth-locked クラスが付く
+          <t>1. 1〜4回目：認証エラーメッセージに残り回数（4,3,2,1）が表示される
+2. 5回目：認証エラーメッセージがロックエラー表示になる
 3. 5回目：ロックメッセージが表示される</t>
         </is>
       </c>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>1. #auth-error に auth-locked クラスが付く
+          <t>1. 認証エラーメッセージがロックエラー表示になる
 2. ロック中メッセージが表示される
 3. ホーム画面へは遷移しない</t>
         </is>
@@ -2638,8 +2638,8 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>1. #screen-pw-change が display:flex になる
-2. ログイン画面（#screen-login）は非表示になる</t>
+          <t>1. パスワード変更画面に切り替わる
+2. ログイン画面は非表示になる</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>・PW変更画面（#screen-pw-change）が表示されている状態</t>
+          <t>・パスワード変更画面が表示されている状態</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -2688,9 +2688,9 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>1. #pw-change-success が visible になる
-2. #btn-change が disabled になる
-3. 2秒後に #screen-login が表示される</t>
+          <t>1. パスワード変更成功メッセージが表示される
+2. 「パスワードを変更する」ボタンが非活性になる
+3. 2秒後にログイン画面が表示される</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
@@ -2739,8 +2739,8 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>1. #err-confirm-password に「パスワードが一致しません」が表示される
-2. API（change-password）は呼び出されない</t>
+          <t>1. 確認パスワードエラーメッセージに「パスワードが一致しません」が表示される
+2. パスワード変更APIは呼び出されない</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
@@ -2787,10 +2787,10 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>1. #screen-login が表示される
-2. #user-id の value が空文字
-3. #password の value が空文字
-4. #auth-error は非表示のまま</t>
+          <t>1. ログイン画面が表示される
+2. ユーザーID入力欄が空になる
+3. パスワード入力欄が空になる
+4. 認証エラーメッセージは非表示のまま</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>1. #add-alert-success が表示される
+          <t>1. ユーザー追加成功アラートが表示される
 2. ユーザー一覧に e2enew001 が追加される
 3. e2enew001 に「有効」バッジが表示される</t>
         </is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>1. #add-alert-error が表示される
+          <t>1. ユーザー追加エラーアラートが表示される
 2. エラーメッセージに「すでに使用されています」が含まれる</t>
         </is>
       </c>
@@ -2941,7 +2941,7 @@
       <c r="F19" s="9" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
-2. e2elocktest のバッジが「ロック中」（badge-locked）になる</t>
+2. e2elocktest のバッジが「ロック中」になる</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       <c r="F20" s="9" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
-2. e2elocktest のバッジが「有効」（badge-active）になる</t>
+2. e2elocktest のバッジが「有効」になる</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
@@ -3038,9 +3038,9 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>1. 成功アラート（#admin-pw-alert-success）が表示される
+          <t>1. 管理者パスワード変更成功アラートが表示される
 2. admin / newadminpw でログインに成功する
-3. /admin.html へリダイレクトされる</t>
+3. 管理画面へリダイレクトされる</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>1. admin 行に「管理者」バッジ（badge-admin）が表示される
+          <t>1. admin 行に「管理者」バッジが表示される
 2. admin 行に削除・ロック・無効化ボタンが表示されない</t>
         </is>
       </c>
@@ -3137,7 +3137,7 @@
       <c r="F23" s="9" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
-2. e2elocktest のバッジが「無効」（badge-inactive）になる</t>
+2. e2elocktest のバッジが「無効」になる</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態（failed_login_count = 0）</t>
+          <t>・user001 が有効状態（ログイン失敗回数がゼロの状態）</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態（failed_login_count = 0）</t>
+          <t>・user001 が有効状態（ログイン失敗回数がゼロの状態）</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">

--- a/login-app/docs/specs-and-testcases.xlsx
+++ b/login-app/docs/specs-and-testcases.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テストケース" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'テストケース'!$A$2:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'テストケース'!$A$2:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,7 +53,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +130,6 @@
         <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE7F6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -255,15 +250,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2036,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.6" customWidth="1" min="1" max="1"/>
@@ -2095,7 +2081,7 @@
       </c>
       <c r="H2" s="22" t="inlineStr">
         <is>
-          <t>対応コード</t>
+          <t>シナリオID</t>
         </is>
       </c>
       <c r="I2" s="22" t="inlineStr">
@@ -2122,9 +2108,9 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態で存在する
-・PW 有効期限が 90 日以内
-・ブラウザでログイン画面を開いている</t>
+          <t>・user001 が有効状態で登録されている
+・パスワード有効期限が90日以内
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -2143,12 +2129,12 @@
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="I3" s="20" t="inlineStr">
@@ -2175,32 +2161,31 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>・admin ユーザーが is_admin=true で存在する
-・ブラウザでログイン画面を開いている</t>
+          <t>・admin が管理者として登録されている
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「admin」を入力
-2. パスワード欄に「root」を入力
+2. パスワード欄に「root1234」を入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>1. URL が /admin.html になる
-2. ページタイトルに「ユーザー管理」が含まれる
-3. ユーザー一覧が表示される</t>
+          <t>1. 管理画面（ユーザー管理画面）に遷移する
+2. ユーザー一覧が表示される</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-ADM-01</t>
+          <t>SC-ADM-01</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
@@ -2227,7 +2212,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>・ブラウザでログイン画面を開いている</t>
+          <t>・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2242,17 +2227,17 @@
           <t>1. ユーザーIDエラーメッセージが表示される
 2. エラー文言が「ユーザーIDを入力してください」
 3. ユーザーID入力欄がエラー表示になる
-4. API 呼び出しは発生しない</t>
+4. 画面遷移は発生しない</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-02</t>
+          <t>SC-02</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -2279,7 +2264,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>・ブラウザでログイン画面を開いている</t>
+          <t>・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2293,17 +2278,17 @@
         <is>
           <t>1. パスワードエラーメッセージが表示される
 2. エラー文言が「パスワードを入力してください」
-3. API 呼び出しは発生しない</t>
+3. 画面遷移は発生しない</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-03</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -2330,13 +2315,13 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>・ブラウザでログイン画面を開いている</t>
+          <t>・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user_invalid」を入力
-2. フォーカスをパスワード欄に移す（blur）</t>
+2. パスワード欄にフォーカスを移す</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -2347,12 +2332,12 @@
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-04</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -2379,13 +2364,13 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>・ブラウザでログイン画面を開いている</t>
+          <t>・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
           <t>1. パスワード欄に「P@ss001」（7文字）を入力
-2. フォーカスを外す（blur）</t>
+2. パスワード欄からフォーカスを外す</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -2396,12 +2381,12 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-05[BV]</t>
+          <t>SC-05-BV-7</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -2428,29 +2413,28 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>・ブラウザでログイン画面を開いている</t>
+          <t>・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>1. パスワード欄に「P@ssw001」（8文字）を入力
-2. フォーカスを外す（blur）</t>
+2. パスワード欄からフォーカスを外す</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>1. パスワードエラーメッセージが表示されない
-2. エラーメッセージが表示されない</t>
+          <t>1. パスワードエラーメッセージが表示されない</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-05[BV-min]</t>
+          <t>SC-05-BV-8</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -2477,12 +2461,15 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態で存在する（ログイン失敗回数がゼロの状態）</t>
+          <t>・user001 が有効状態で登録されており、一度もログイン失敗していない
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>1. ユーザーID「user001」/ パスワード「wrongpass」でログイン</t>
+          <t>1. ユーザーID欄に「user001」を入力
+2. パスワード欄に誤ったパスワードを入力
+3. ログインボタンをクリック</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -2494,12 +2481,12 @@
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-06</t>
+          <t>SC-06</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -2526,33 +2513,34 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>・e2elock が有効状態で存在する（ログイン失敗回数がゼロの状態）</t>
+          <t>・e2elock が有効状態で登録されており、一度もログイン失敗していない
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>1. e2elock / 誤PW でログイン（1回目）→ 残り4回確認
-2. e2elock / 誤PW でログイン（2回目）→ 残り3回確認
-3. e2elock / 誤PW でログイン（3回目）→ 残り2回確認
-4. e2elock / 誤PW でログイン（4回目）→ 残り1回確認
-5. e2elock / 誤PW でログイン（5回目）</t>
+          <t>1. e2elock / 誤パスワードでログイン（1回目）→ 残り4回のメッセージを確認
+2. e2elock / 誤パスワードでログイン（2回目）→ 残り3回のメッセージを確認
+3. e2elock / 誤パスワードでログイン（3回目）→ 残り2回のメッセージを確認
+4. e2elock / 誤パスワードでログイン（4回目）→ 残り1回のメッセージを確認
+5. e2elock / 誤パスワードでログイン（5回目）</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
           <t>1. 1〜4回目：認証エラーメッセージに残り回数（4,3,2,1）が表示される
 2. 5回目：認証エラーメッセージがロックエラー表示になる
-3. 5回目：ロックメッセージが表示される</t>
+3. 5回目：アカウントロック中のメッセージが表示される</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-07</t>
+          <t>SC-07</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -2579,7 +2567,8 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>・e2elock がロック状態で存在する（locked_until が未来の日時）</t>
+          <t>・e2elock がロック状態で登録されている
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -2590,18 +2579,18 @@
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>1. 認証エラーメッセージがロックエラー表示になる
-2. ロック中メッセージが表示される
+2. アカウントロック中のメッセージが表示される
 3. ホーム画面へは遷移しない</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-08</t>
+          <t>SC-08</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -2618,7 +2607,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>PW期限切れ → 変更画面遷移</t>
+          <t>パスワード期限切れ → 変更画面遷移</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -2628,7 +2617,8 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>・e2eexpired が有効状態で存在する（password_changed_at が 91 日以上前）</t>
+          <t>・e2eexpired が有効状態で登録されており、パスワード最終変更から91日以上経過している
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2644,12 +2634,12 @@
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-09</t>
+          <t>SC-09</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
@@ -2666,7 +2656,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>PW変更成功と自動遷移</t>
+          <t>パスワード変更成功と自動遷移</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2676,7 +2666,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>・パスワード変更画面が表示されている状態</t>
+          <t>・パスワード変更画面が表示されている</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -2695,12 +2685,12 @@
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-10</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
@@ -2717,7 +2707,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>PW変更 - 確認PW不一致エラー</t>
+          <t>パスワード変更 - 確認パスワード不一致エラー</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -2727,7 +2717,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>・PW変更画面が表示されている状態</t>
+          <t>・パスワード変更画面が表示されている</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2740,17 +2730,17 @@
       <c r="F15" s="9" t="inlineStr">
         <is>
           <t>1. 確認パスワードエラーメッセージに「パスワードが一致しません」が表示される
-2. パスワード変更APIは呼び出されない</t>
+2. 画面遷移は発生しない</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-12</t>
+          <t>SC-12</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
@@ -2795,12 +2785,12 @@
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/login.spec.js &gt; SC-11</t>
+          <t>SC-11</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
@@ -2828,7 +2818,7 @@
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>・管理画面が表示されている
-・e2enew001 が DB に存在しない</t>
+・e2enew001 がシステムに登録されていない</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2840,19 +2830,19 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>1. ユーザー追加成功アラートが表示される
+          <t>1. ユーザー追加成功メッセージが表示される
 2. ユーザー一覧に e2enew001 が追加される
 3. e2enew001 に「有効」バッジが表示される</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-A01</t>
+          <t>SC-A01</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -2879,7 +2869,8 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>・user001 が DB に存在する</t>
+          <t>・user001 がシステムに登録されている
+・管理画面が表示されている</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -2891,18 +2882,18 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>1. ユーザー追加エラーアラートが表示される
+          <t>1. ユーザー追加エラーメッセージが表示される
 2. エラーメッセージに「すでに使用されています」が含まれる</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-A02</t>
+          <t>SC-A02</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
@@ -2929,7 +2920,8 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>・e2elocktest が有効状態で存在する</t>
+          <t>・e2elocktest が有効状態で登録されている
+・管理画面が表示されている</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2946,12 +2938,12 @@
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-A05</t>
+          <t>SC-A05</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
@@ -2978,7 +2970,8 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>・e2elocktest がロック状態で存在する</t>
+          <t>・e2elocktest がロック状態で登録されている
+・管理画面が表示されている</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -2994,12 +2987,12 @@
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-A06</t>
+          <t>SC-A06</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
@@ -3031,26 +3024,27 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>1. 管理者PW変更カードの入力欄に「newadminpw」を入力
+          <t>1. 管理者パスワード変更欄に「NewAdminPw1!」を入力
 2. 「変更する」ボタンをクリック
-3. ログイン画面で admin / newadminpw でログインする</t>
+3. ログアウトしてログイン画面を開く
+4. admin / NewAdminPw1! でログインする</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>1. 管理者パスワード変更成功アラートが表示される
-2. admin / newadminpw でログインに成功する
-3. 管理画面へリダイレクトされる</t>
+          <t>1. 管理者パスワード変更成功メッセージが表示される
+2. 新しいパスワードでログインに成功する
+3. 管理画面に遷移する</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-ADM-02</t>
+          <t>SC-ADM-02</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -3067,7 +3061,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>管理者：管理者バッジ表示・保護確認</t>
+          <t>管理者：管理者バッジ表示・操作保護確認</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -3082,7 +3076,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>1. ユーザー一覧を確認する</t>
+          <t>1. ユーザー一覧の admin 行を確認する</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -3093,12 +3087,12 @@
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-ADM-03</t>
+          <t>SC-ADM-03</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -3125,7 +3119,8 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>・e2elocktest が有効状態で存在する</t>
+          <t>・e2elocktest が有効状態で登録されている
+・管理画面が表示されている</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -3142,12 +3137,12 @@
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>Playwright E2E</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>tests/e2e/admin.spec.js &gt; SC-A09</t>
+          <t>SC-A09</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -3157,246 +3152,241 @@
       </c>
     </row>
     <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>TC-P01</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/auth/login - 正常ログイン</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>正常系（API）</t>
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>TC-S01</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>ログアウト後のセッション無効化確認</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態で存在する（PW期限内）</t>
+          <t>・user001 でログイン済み（ホーム画面表示中）</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/login
-   body: { userId: 'user001', password: 'P@ssword' }</t>
+          <t>1. ログアウトボタンをクリックする
+2. ブラウザの戻るボタンを押してホーム画面への戻りを試みる</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>1. HTTP 200
-2. body.data.userId === 'user001'
-3. body.data.isAdmin === false</t>
+          <t>1. ログイン画面が表示される
+2. ホーム画面のコンテンツは表示されない</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>Playwright API</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>tests/auth.spec.js &gt; TC-L01</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
+          <t>SC-SEC-01</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>TC-S02</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>不正なユーザーIDでのログイン試行</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>セキュリティ</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>・ログイン画面を開いている</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>1. ユーザーID欄に「' OR '1'='1」を入力
+2. パスワード欄に任意の文字列を入力
+3. ログインボタンをクリック</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>1. ログインが拒否される（ホーム画面に遷移しない）
+2. 他のユーザー情報は表示されない</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>自社ツール（E2E）</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>SC-SEC-02</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>TC-P02</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/auth/login - 管理者ログイン</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>正常系（API）</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>・admin が is_admin=true で存在する</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>1. POST /api/auth/login
-   body: { userId: 'admin', password: 'root' }</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>1. HTTP 200
-2. body.data.isAdmin === true</t>
-        </is>
-      </c>
-      <c r="G25" s="25" t="inlineStr">
-        <is>
-          <t>Playwright API</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>tests/auth.spec.js &gt; TC-ADM-L01</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-    </row>
     <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>TC-P03</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>POST /api/auth/login - PW不一致（1回目）</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>異常系（API）</t>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>TC-B01</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>パスワード変更後89日目のログイン（期限内）</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>境界値</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態（ログイン失敗回数がゼロの状態）</t>
+          <t>・e2eexpiry89 が登録されており、パスワード最終変更から89日経過している
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/login
-   body: { userId: 'user001', password: 'wrong' }</t>
+          <t>1. e2eexpiry89 / 正しいパスワードでログインする</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>1. HTTP 401
-2. body.error.code === 'AUTH_FAILED'
-3. body.error.remainingAttempts === 4</t>
+          <t>1. ホーム画面に切り替わる（パスワード変更画面には遷移しない）</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>Playwright API</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>tests/auth.spec.js &gt; TC-L03</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>SC-BV-PW-89</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>TC-P04</t>
+          <t>TC-B02</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>POST /api/auth/login - 5回失敗でロック</t>
+          <t>パスワード変更後90日目のログイン（期限切れ）</t>
         </is>
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>境界値（API）</t>
+          <t>境界値</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>・user001 が有効状態（ログイン失敗回数がゼロの状態）</t>
+          <t>・e2eexpiry90 が登録されており、パスワード最終変更から90日経過している
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>1〜4回: POST /api/auth/login（誤PW）→ 401 確認
-5回目: POST /api/auth/login（誤PW）</t>
+          <t>1. e2eexpiry90 / 正しいパスワードでログインする</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>5回目:
-1. HTTP 403
-2. body.error.code === 'ACCOUNT_LOCKED'
-3. body.error.lockedUntil が設定される</t>
+          <t>1. パスワード変更画面に切り替わる（ホーム画面には遷移しない）</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>Playwright API</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>tests/auth.spec.js &gt; TC-L04〜L08</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>最高</t>
+          <t>SC-BV-PW-90</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>
     <row r="28" ht="80" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>TC-P05</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/auth/logout - セッション無効化</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>正常系（API）</t>
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>TC-B03</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>ロック期限1分以上残っている状態でのログイン拒否</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>境界値</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>・user001 でログイン済み（有効なセッション）</t>
+          <t>・e2elock がロック状態で登録されており、ロック解除まで1分以上ある
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/logout
-2. GET /api/auth/status</t>
+          <t>1. e2elock / 正しいパスワードでログインを試みる</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>1. ログアウト: HTTP 200
-2. status 確認: HTTP 401</t>
+          <t>1. アカウントロック中のメッセージが表示される
+2. ホーム画面へは遷移しない</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>Playwright API</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>tests/auth.spec.js &gt; TC-LO01/LO02</t>
+          <t>SC-BV-LOCK-1MIN</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
@@ -3406,344 +3396,55 @@
       </c>
     </row>
     <row r="29" ht="80" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>TC-P06</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>PUT /api/admin/password - 管理者PW変更</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>正常系（API）</t>
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>TC-B04</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>ロック期限経過後のログイン成功</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>境界値</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>・admin ユーザーが is_admin=true で存在する</t>
+          <t>・e2elock のロック期限が1分前に経過している
+・ログイン画面を開いている</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>1. PUT /api/admin/password
-   body: { password: 'newpw' }
-2. POST /api/auth/login（admin / newpw）</t>
+          <t>1. e2elock / 正しいパスワードでログインする</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>1. HTTP 200
-2. body.status === 'success'
-3. 新PWでのログインが成功（HTTP 200）</t>
+          <t>1. ホーム画面に切り替わる（ロックエラーは表示されない）</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>Playwright API</t>
+          <t>自社ツール（E2E）</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>tests/auth.spec.js &gt; TC-ADM-PW01</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="80" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>TC-U01</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>isPasswordExpired - 89日前（境界値-1）</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>境界値（Unit）</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>・utils.js の isPasswordExpired 関数</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>1. isPasswordExpired(89日前の Date) を呼び出す</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>1. 戻り値が false</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="inlineStr">
-        <is>
-          <t>Jest Unit</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>tests/unit/utils.test.js &gt; BV-03</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="80" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>TC-U02</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>isPasswordExpired - 90日前（境界値）</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>境界値（Unit）</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>・utils.js の isPasswordExpired 関数</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>1. isPasswordExpired(90日前の Date) を呼び出す</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>1. 戻り値が true</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>Jest Unit</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>tests/unit/utils.test.js &gt; BV-04</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
+          <t>SC-BV-LOCK-EXPIRED</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="80" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>TC-U03</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>isLocked - ロック中（1分後）</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>境界値（Unit）</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>・utils.js の isLocked 関数</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>1. isLocked(1分後の Date) を呼び出す</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>1. 戻り値が true</t>
-        </is>
-      </c>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>Jest Unit</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>tests/unit/utils.test.js &gt; BV-15</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="80" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>TC-U04</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>isLocked - ロック期限切れ（1分前）</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>境界値（Unit）</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>・utils.js の isLocked 関数</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>1. isLocked(1分前の Date) を呼び出す</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>1. 戻り値が false</t>
-        </is>
-      </c>
-      <c r="G33" s="25" t="inlineStr">
-        <is>
-          <t>Jest Unit</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>tests/unit/utils.test.js &gt; BV-13</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="80" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>TC-S01</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>SQLインジェクション耐性（ユーザーID）</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>セキュリティ</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>・DB が稼働している</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>1. POST /api/auth/login
-   body: { userId: "' OR '1'='1", password: 'any' }</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>1. HTTP 400 または 401
-2. 全ユーザーが返却されない
-3. DB が改ざんされない（GET /api/users で確認）</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>Playwright API</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>tests/auth.spec.js &gt; TC-SEC-01</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="80" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>TC-S02</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>ログアウト後の保護API拒否</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="inlineStr">
-        <is>
-          <t>セキュリティ</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>・ログアウト済み（セッションなし）</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>1. GET /api/auth/status を送信する</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>1. HTTP 401
-2. body.error.code === 'UNAUTHORIZED'</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>Playwright API</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>tests/auth.spec.js &gt; TC-ST02</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:I35"/>
+  <autoFilter ref="A2:I29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>

--- a/login-app/docs/specs-and-testcases.xlsx
+++ b/login-app/docs/specs-and-testcases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,13 @@
       <name val="メイリオ"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="001F4E79"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +98,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -180,25 +195,31 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -207,7 +228,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,10 +237,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,10 +273,10 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -923,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -979,7 +1000,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 / isAdmin=false</t>
+          <t>ログイン成功（一般ユーザー）</t>
         </is>
       </c>
     </row>
@@ -996,12 +1017,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>管理画面（/admin.html）</t>
+          <t>管理画面</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>HTTP 200 / isAdmin=true → window.location.href</t>
+          <t>ログイン成功（管理者）→ 別ページへ遷移</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1034,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>PW期限切れ（HTTP 422）</t>
+          <t>パスワード期限切れ</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PW変更画面</t>
+          <t>パスワード変更画面</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>PASSWORD_EXPIRED コード</t>
+          <t>90日以上変更なし → 変更画面へ誘導</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1056,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>認証失敗（HTTP 401）</t>
+          <t>認証失敗</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1057,7 +1078,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>アカウントロック（HTTP 403）</t>
+          <t>アカウントロック</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1067,7 +1088,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ロック残り時間を表示</t>
+          <t>ロックエラーメッセージを表示</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1117,12 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>PW変更画面</t>
+          <t>パスワード変更画面</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>PW変更成功（HTTP 200）</t>
+          <t>パスワード変更成功</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1111,14 +1132,14 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>成功メッセージ → ボタン disabled → 2秒タイマー</t>
+          <t>成功メッセージ表示 → 2秒後に自動遷移</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>PW変更画面</t>
+          <t>パスワード変更画面</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1128,24 +1149,24 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>PW変更画面（エラー表示）</t>
+          <t>パスワード変更画面（エラー表示）</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>API呼び出しなし</t>
+          <t>画面内でエラー表示</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>管理画面</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>各ユーザー管理操作</t>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ユーザー管理操作</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1155,13 +1176,37 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>PUT/DELETE 後に loadUsers() 再実行</t>
+          <t>操作後にユーザー一覧を再取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>【Mermaid 図コード — GitHub / VS Code / Mermaid Live Editor でレンダリング可能】
+```mermaid
+flowchart TD
+    LOGIN["ログイン画面\nSCR-001"]
+    HOME["ホーム画面\nSCR-002"]
+    PWCHANGE["パスワード変更画面\nSCR-003"]
+    ADMIN["管理画面\nSCR-004"]
+    LOGIN --&gt;|一般ユーザーログイン成功| HOME
+    LOGIN --&gt;|管理者ログイン成功| ADMIN
+    LOGIN --&gt;|パスワード期限切れ| PWCHANGE
+    LOGIN --&gt;|認証失敗| LOGIN
+    LOGIN --&gt;|アカウントロック| LOGIN
+    HOME --&gt;|ログアウト| LOGIN
+    PWCHANGE --&gt;|パスワード変更成功（2秒後）| LOGIN
+    PWCHANGE --&gt;|バリデーションエラー| PWCHANGE
+    ADMIN --&gt;|ユーザー管理操作| ADMIN
+```</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1173,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1207,233 +1252,255 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>DB変化 / 備考</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>連続5回認証失敗</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>ロック中（locked）</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>ログイン連続失敗回数が5回に達し、ロック期限が設定される</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>管理者が手動ロック</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>ロック中（locked）</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ロック期限が永続（9999-12-31）に設定される</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>管理者が無効化</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>無効（inactive）</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>アカウントが無効化される</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>PW未変更から90日経過</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PW期限切れ（expired_pw）</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>次回ログイン時にチェック、状態は有効のまま</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>ロック中（locked）</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>30分後（自動）</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>ロック期限が過去になり、失敗回数がリセットされる</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ロック中（locked）</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>管理者がロック解除</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>ロック期限が解除され、失敗回数がリセットされる</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>無効（inactive）</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>管理者が有効化</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>アカウントが有効化される</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>PW期限切れ</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>ユーザーがPW変更</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>パスワード変更日時が現在時刻に更新される</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>PW期限切れ</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>管理者がPW変更要求</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>有効（active）</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>次回ログイン時にパスワード変更画面へ誘導される</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>管理者（admin）</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>管理者PW変更フォームで変更</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>管理者（admin）</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>管理者フラグは変化しない。パスワードのみ更新される</t>
         </is>
       </c>
     </row>
+    <row r="14" ht="200" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>【Mermaid 図コード — GitHub / VS Code / Mermaid Live Editor でレンダリング可能】
+```mermaid
+stateDiagram-v2
+    [*] --&gt; 有効
+    有効 --&gt; ロック中 : 連続5回認証失敗
+    有効 --&gt; ロック中 : 管理者が手動ロック
+    有効 --&gt; 無効 : 管理者が無効化
+    有効 --&gt; PW期限切れ : パスワード変更から90日経過
+    ロック中 --&gt; 有効 : 30分後（自動解除）
+    ロック中 --&gt; 有効 : 管理者がロック解除
+    無効 --&gt; 有効 : 管理者が有効化
+    PW期限切れ --&gt; 有効 : ユーザーがパスワード変更
+    PW期限切れ --&gt; 有効 : 管理者がパスワード変更要求
+    管理者 --&gt; 管理者 : 管理者パスワード変更のみ可
+```</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1502,17 +1569,17 @@
       </c>
     </row>
     <row r="3" ht="65" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>US-01</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1522,36 +1589,36 @@
           <t>社員として、正しい ID とパスワードでログインしてホーム画面を表示したい</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Given user001 が有効状態で PW 期限内で存在する
 When ログイン画面で user001 / P@ssword を入力してログインボタンを押す
 Then ホーム画面が表示され「user001 さん」とログイン日時が表示される</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>US-02</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1561,36 +1628,36 @@
           <t>管理者として、admin / root でログインすると管理画面に遷移したい</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Given admin ユーザーが is_admin=true で存在する
 When ログイン画面で admin / root を入力してログインボタンを押す
 Then /admin.html へリダイレクトされ管理画面が表示される</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>SC-ADM-01（新規）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>US-03</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1600,36 +1667,36 @@
           <t>社員として、誤ったパスワードを入力したとき残り試行回数を確認したい</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Given user001 が有効状態で存在する
 When 誤ったパスワードでログインする（1回目）
 Then 「あと4回失敗するとロックされます」が表示される</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>US-04</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -1639,36 +1706,36 @@
           <t>社員として、5回連続でパスワードを間違えたとき、アカウントがロックされることを認識したい</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Given e2elock が有効状態で存在する
 When 誤ったパスワードでログインを5回繰り返す
 Then 5回目にロックメッセージが表示され、正しいパスワードでもログインできなくなる</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>US-05</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1678,36 +1745,36 @@
           <t>社員として、パスワードが期限切れのとき変更画面に案内されたい</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Given e2eexpired の PW 変更日が 91 日以上前
 When e2eexpired / 正しい PW でログインする
 Then パスワード変更画面が表示される</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>SC-09</t>
         </is>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>US-06</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1717,36 +1784,36 @@
           <t>社員として、パスワード変更画面で新しいパスワードを設定してログイン画面に戻りたい</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Given PW 変更画面が表示されている
 When 新 PW「NewPass1!」と確認 PW「NewPass1!」を入力して変更ボタンを押す
 Then 成功メッセージが表示され、2秒後にログイン画面へ遷移する</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>SC-10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>US-07</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1756,36 +1823,36 @@
           <t>社員として、ログアウトするとログイン画面に戻り入力欄がクリアされることを確認したい</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Given user001 でログイン済み
 When ログアウトボタンを押す
 Then ログイン画面が表示され、ユーザーID・PW欄が空になる</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>SC-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>US-08</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1795,36 +1862,36 @@
           <t>社員として、ユーザーID が未入力のまま送信したときエラーを知りたい</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Given ログイン画面が表示されている
 When ユーザーIDを空のままログインボタンを押す
 Then 「ユーザーIDを入力してください」が #err-userid に表示される</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>US-09</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>一般ユーザー</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1834,36 +1901,36 @@
           <t>社員として、パスワードが 7 文字（最小値-1）のとき文字数エラーを知りたい</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Given ログイン画面が表示されている
 When PW欄に 7文字のパスワードを入力しフォーカスを外す
 Then 「パスワードは8〜32文字で入力してください」が表示される</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/login.spec.js</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>SC-05</t>
         </is>
       </c>
     </row>
     <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>US-10</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1873,36 +1940,36 @@
           <t>管理者として、新しい社員アカウントを安全に作成したい</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Given 管理画面が表示されている
 When 未使用ID と有効なPW を入力して追加ボタンを押す
 Then 成功メッセージが表示され、ユーザー一覧に新ユーザーが追加される</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/admin.spec.js</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>SC-A01</t>
         </is>
       </c>
     </row>
     <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>US-11</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1912,36 +1979,36 @@
           <t>管理者として、ロックされた社員のアカウントをすぐに解除したい</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Given e2elocktest がロック状態で存在する
 When ロック解除ボタンをクリックする
 Then badge-active バッジが表示され、失敗カウントが 0 にリセットされる</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/admin.spec.js</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>SC-A06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>US-12</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1951,36 +2018,36 @@
           <t>管理者として、管理者パスワードを専用フォームから変更したい</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Given 管理画面が表示されている
 When 管理者PW変更カードに「newadminpw」を入力して変更ボタンを押す
 Then 成功メッセージが表示され、newadminpw で admin ログインが成功する</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/admin.spec.js</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>SC-ADM-02（新規）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>US-13</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1990,19 +2057,19 @@
           <t>管理者として、退職者のアカウントを削除または無効化したい</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Given e2edelete / e2elocktest が有効状態で存在する
 When 削除ボタン または 無効化ボタンをクリックする
 Then 一覧から消える（削除）/ badge-inactive バッジが表示される（無効化）</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>tests/e2e/admin.spec.js</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>SC-A09 / SC-A11</t>
         </is>
@@ -2044,185 +2111,185 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>テストケースID</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>テスト名</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>テスト区分</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>前提条件（Preconditions）</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>検証手順（Steps）</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>期待値（Expected Results）</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>自動化手段</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>シナリオID</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>TC-E01</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>一般ユーザー正常ログイン</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>・user001 が有効状態で登録されている
 ・パスワード有効期限が90日以内
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user001」を入力
 2. パスワード欄に「P@ssword」を入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>1. ホーム画面に切り替わる
 2. ホーム画面のユーザー名表示が「user001 さん」になる
 3. ログイン成功メッセージが表示される</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>TC-E02</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>管理者ログイン → 管理画面遷移</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>・admin が管理者として登録されている
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「admin」を入力
 2. パスワード欄に「root1234」を入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>1. 管理画面（ユーザー管理画面）に遷移する
 2. ユーザー一覧が表示される</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>SC-ADM-01</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>TC-E03</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>ユーザーID未入力バリデーション</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄を空のままにする
 2. パスワード欄に「P@ssword」を入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーIDエラーメッセージが表示される
 2. エラー文言が「ユーザーIDを入力してください」
@@ -2230,294 +2297,294 @@
 4. 画面遷移は発生しない</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>TC-E04</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>パスワード未入力バリデーション</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user001」を入力
 2. パスワード欄を空のままにする
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>1. パスワードエラーメッセージが表示される
 2. エラー文言が「パスワードを入力してください」
 3. 画面遷移は発生しない</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>SC-03</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>TC-E05</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>記号含むユーザーID バリデーション</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user_invalid」を入力
 2. パスワード欄にフォーカスを移す</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーIDエラーメッセージが表示される
 2. エラー文言が「ユーザーIDは半角英数字で入力してください」</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>TC-E06</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>パスワード 7文字（最小値-1）バリデーション</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>1. パスワード欄に「P@ss001」（7文字）を入力
 2. パスワード欄からフォーカスを外す</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>1. パスワードエラーメッセージが表示される
 2. エラー文言が「パスワードは8〜32文字で入力してください」</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>SC-05-BV-7</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>TC-E07</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>パスワード 8文字（最小値）バリデーション</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>1. パスワード欄に「P@ssw001」（8文字）を入力
 2. パスワード欄からフォーカスを外す</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>1. パスワードエラーメッセージが表示されない</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>SC-05-BV-8</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>TC-E08</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>認証失敗 - 残り試行回数表示（1回目）</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>・user001 が有効状態で登録されており、一度もログイン失敗していない
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user001」を入力
 2. パスワード欄に誤ったパスワードを入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>1. 認証エラーメッセージが表示される
 2. テキストに「あと4回失敗するとロックされます」が含まれる
 3. ロックエラー表示にはなっていない</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>TC-E09</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>5回連続失敗でアカウントロック</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>・e2elock が有効状態で登録されており、一度もログイン失敗していない
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>1. e2elock / 誤パスワードでログイン（1回目）→ 残り4回のメッセージを確認
 2. e2elock / 誤パスワードでログイン（2回目）→ 残り3回のメッセージを確認
@@ -2526,256 +2593,256 @@
 5. e2elock / 誤パスワードでログイン（5回目）</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>1. 1〜4回目：認証エラーメッセージに残り回数（4,3,2,1）が表示される
 2. 5回目：認証エラーメッセージがロックエラー表示になる
 3. 5回目：アカウントロック中のメッセージが表示される</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>TC-E10</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>ロック中のログイン拒否</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>・e2elock がロック状態で登録されている
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>1. e2elock / 正しいパスワードでログインを試みる</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>1. 認証エラーメッセージがロックエラー表示になる
 2. アカウントロック中のメッセージが表示される
 3. ホーム画面へは遷移しない</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>TC-E11</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>パスワード期限切れ → 変更画面遷移</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>・e2eexpired が有効状態で登録されており、パスワード最終変更から91日以上経過している
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>1. e2eexpired / 正しいパスワードでログインする</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>1. パスワード変更画面に切り替わる
 2. ログイン画面は非表示になる</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>SC-09</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>TC-E12</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>パスワード変更成功と自動遷移</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>・パスワード変更画面が表示されている</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>1. 新しいパスワード欄に「NewPass1!」を入力
 2. 確認パスワード欄に「NewPass1!」を入力
 3. 「パスワードを変更する」ボタンをクリック</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>1. パスワード変更成功メッセージが表示される
 2. 「パスワードを変更する」ボタンが非活性になる
 3. 2秒後にログイン画面が表示される</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>SC-10</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>TC-E13</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>パスワード変更 - 確認パスワード不一致エラー</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>・パスワード変更画面が表示されている</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>1. 新しいパスワード欄に「NewPass1!」を入力
 2. 確認パスワード欄に「DifferentPass1!」を入力
 3. 「パスワードを変更する」ボタンをクリック</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>1. 確認パスワードエラーメッセージに「パスワードが一致しません」が表示される
 2. 画面遷移は発生しない</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>SC-12</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>TC-E14</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>ログアウトとフォームクリア</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>・user001 でログイン済み（ホーム画面表示中）</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>1. ログアウトボタンをクリックする</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>1. ログイン画面が表示される
 2. ユーザーID入力欄が空になる
@@ -2783,246 +2850,246 @@
 4. 認証エラーメッセージは非表示のまま</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>SC-11</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>TC-A01</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>管理者：ユーザー追加成功</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>・管理画面が表示されている
 ・e2enew001 がシステムに登録されていない</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「e2enew001」を入力
 2. パスワード欄に「NewPass1!」を入力
 3. 「追加」ボタンをクリック</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>1. ユーザー追加成功メッセージが表示される
 2. ユーザー一覧に e2enew001 が追加される
 3. e2enew001 に「有効」バッジが表示される</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>SC-A01</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="18" ht="80" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>TC-A02</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>管理者：ID重複エラー</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>異常系</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>・user001 がシステムに登録されている
 ・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「user001」を入力
 2. パスワード欄に「NewPass1!」を入力
 3. 「追加」ボタンをクリック</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>1. ユーザー追加エラーメッセージが表示される
 2. エラーメッセージに「すでに使用されています」が含まれる</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>SC-A02</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="19" ht="80" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>TC-A03</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>管理者：手動ロック</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>・e2elocktest が有効状態で登録されている
 ・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>1. e2elocktest の「ロックする」ボタンをクリック
 2. 確認ダイアログで「OK」をクリック</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
 2. e2elocktest のバッジが「ロック中」になる</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>SC-A05</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>TC-A04</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>管理者：ロック解除</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>・e2elocktest がロック状態で登録されている
 ・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>1. e2elocktest の「ロック解除」ボタンをクリック</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
 2. e2elocktest のバッジが「有効」になる</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>SC-A06</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>TC-A05</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>管理者：管理者パスワード変更</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>1. 管理者パスワード変更欄に「NewAdminPw1!」を入力
 2. 「変更する」ボタンをクリック
@@ -3030,414 +3097,414 @@
 4. admin / NewAdminPw1! でログインする</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>1. 管理者パスワード変更成功メッセージが表示される
 2. 新しいパスワードでログインに成功する
 3. 管理画面に遷移する</t>
         </is>
       </c>
-      <c r="G21" s="25" t="inlineStr">
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>SC-ADM-02</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="22" ht="80" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>TC-A06</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>管理者：管理者バッジ表示・操作保護確認</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>1. ユーザー一覧の admin 行を確認する</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>1. admin 行に「管理者」バッジが表示される
 2. admin 行に削除・ロック・無効化ボタンが表示されない</t>
         </is>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>SC-ADM-03</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="23" ht="80" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>TC-A07</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>管理者：ユーザー無効化</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>正常系</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>・e2elocktest が有効状態で登録されている
 ・管理画面が表示されている</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>1. e2elocktest の「無効化」ボタンをクリック
 2. 確認ダイアログで「OK」をクリック</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>1. 成功メッセージが表示される
 2. e2elocktest のバッジが「無効」になる</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>SC-A09</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>TC-S01</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>ログアウト後のセッション無効化確認</t>
         </is>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>セキュリティ</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>・user001 でログイン済み（ホーム画面表示中）</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>1. ログアウトボタンをクリックする
 2. ブラウザの戻るボタンを押してホーム画面への戻りを試みる</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>1. ログイン画面が表示される
 2. ホーム画面のコンテンツは表示されない</t>
         </is>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>SC-SEC-01</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>TC-S02</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>不正なユーザーIDでのログイン試行</t>
         </is>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>セキュリティ</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>1. ユーザーID欄に「' OR '1'='1」を入力
 2. パスワード欄に任意の文字列を入力
 3. ログインボタンをクリック</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>1. ログインが拒否される（ホーム画面に遷移しない）
 2. 他のユーザー情報は表示されない</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>SC-SEC-02</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
     </row>
     <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>TC-B01</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>パスワード変更後89日目のログイン（期限内）</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>・e2eexpiry89 が登録されており、パスワード最終変更から89日経過している
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>1. e2eexpiry89 / 正しいパスワードでログインする</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>1. ホーム画面に切り替わる（パスワード変更画面には遷移しない）</t>
         </is>
       </c>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>SC-BV-PW-89</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
     <row r="27" ht="80" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>TC-B02</t>
         </is>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>パスワード変更後90日目のログイン（期限切れ）</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>・e2eexpiry90 が登録されており、パスワード最終変更から90日経過している
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>1. e2eexpiry90 / 正しいパスワードでログインする</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>1. パスワード変更画面に切り替わる（ホーム画面には遷移しない）</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="G27" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>SC-BV-PW-90</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="28" ht="80" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>TC-B03</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>ロック期限1分以上残っている状態でのログイン拒否</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>・e2elock がロック状態で登録されており、ロック解除まで1分以上ある
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>1. e2elock / 正しいパスワードでログインを試みる</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>1. アカウントロック中のメッセージが表示される
 2. ホーム画面へは遷移しない</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>SC-BV-LOCK-1MIN</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
     <row r="29" ht="80" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>TC-B04</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>ロック期限経過後のログイン成功</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>境界値</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>・e2elock のロック期限が1分前に経過している
 ・ログイン画面を開いている</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>1. e2elock / 正しいパスワードでログインする</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>1. ホーム画面に切り替わる（ロックエラーは表示されない）</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="G29" s="27" t="inlineStr">
         <is>
           <t>自社ツール（E2E）</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>SC-BV-LOCK-EXPIRED</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>高</t>
         </is>
